--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>72193622</v>
       </c>
       <c r="B2" t="n">
-        <v>96309</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485661.7774428688</v>
+        <v>485662</v>
       </c>
       <c r="R2" t="n">
-        <v>6596399.019764927</v>
+        <v>6596399</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,19 +755,9 @@
           <t>2018-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,313 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135461398</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillagen, NO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485347</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6596455</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135461399</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillagen, NO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485347</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6596455</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135461388</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107801</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223653</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig hässleklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula latifolia var. latifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillagen, NO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485336</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596536</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72193622</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135461398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135461399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135461388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135461398</v>
       </c>
       <c r="B3" t="n">
-        <v>101324</v>
+        <v>101372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135461399</v>
       </c>
       <c r="B4" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>135461388</v>
       </c>
       <c r="B5" t="n">
-        <v>107801</v>
+        <v>107856</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135461398</v>
       </c>
       <c r="B3" t="n">
-        <v>101372</v>
+        <v>101399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135461399</v>
       </c>
       <c r="B4" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>135461388</v>
       </c>
       <c r="B5" t="n">
-        <v>107856</v>
+        <v>107883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135461388</v>
+        <v>135461398</v>
       </c>
       <c r="B3" t="n">
-        <v>107883</v>
+        <v>101404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,35 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223653</v>
+        <v>222782</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig hässleklocka</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula latifolia var. latifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillagen, NO om, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485336</v>
+        <v>485347</v>
       </c>
       <c r="R3" t="n">
-        <v>6596536</v>
+        <v>6596455</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +879,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -896,6 +895,221 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135461398</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135461399</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillagen, NO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485347</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6596455</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135461399</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135461388</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107888</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223653</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig hässleklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula latifolia var. latifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillagen, NO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485336</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596536</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135461388</t>
         </is>
@@ -905,6 +1119,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135461398</v>
       </c>
       <c r="B3" t="n">
-        <v>101404</v>
+        <v>101406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135461399</v>
       </c>
       <c r="B4" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>135461388</v>
       </c>
       <c r="B5" t="n">
-        <v>107888</v>
+        <v>107890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43148-2025 artfynd.xlsx
+++ b/artfynd/A 43148-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135461398</v>
       </c>
       <c r="B3" t="n">
-        <v>101406</v>
+        <v>101423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135461399</v>
       </c>
       <c r="B4" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>135461388</v>
       </c>
       <c r="B5" t="n">
-        <v>107890</v>
+        <v>107913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
